--- a/L2-GA-140020-0301.01.3-硬伤清单.xlsx
+++ b/L2-GA-140020-0301.01.3-硬伤清单.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="硬伤" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'硬伤'!$A$1:$D$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'硬伤'!$A$1:$D$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -530,67 +530,48 @@
       </c>
     </row>
     <row r="4" ht="72" customHeight="1">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>3.2.1 第 (3) 类</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>postcapping DMF wash step using DMF is replaced by direct charging</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>终版 PVP 仍在封端后用 DMF 洗涤树脂，封端液是在 R22 配制后再转入 Sy15，并搅拌至少 5 min。这句把封端后的 DMF 洗涤写成改成直接投入合成釜，和终版工艺不一致。请改成：封端液在 TJ4S-1213-R22 配制，至少搅拌 5 min，再转入 TJ4S-1213-Sy15；封端后的 DMF 洗涤仍按终版执行。</t>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Step 2 质量标准表，多处完成时间</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>PV Step2 star</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Completion prior to PV Step2 star 少了 t，至少 11 处，应为 start。Assay 的非放行侧是 ≥80.0% 且 ≤110.0% w/w，PPQ 侧只剩 ≥80.0% w/w。IPAc 的 PPQ 限度是 ≤5000，没有 ppm，另一列有 ppm；吡啶两侧都是 ≤5000，没有单位。请补 start，并确认 Assay 上限和 ppm 是有意取消还是列错。</t>
         </is>
       </c>
     </row>
     <row r="5" ht="72" customHeight="1">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Step 2 质量标准表，多处完成时间</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>PV Step2 star</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Completion prior to PV Step2 star 少了 t，至少 11 处，应为 start。Assay 的非放行侧是 ≥80.0% 且 ≤110.0% w/w，PPQ 侧只剩 ≥80.0% w/w。IPAc 的 PPQ 限度是 ≤5000，没有 ppm，另一列有 ppm；吡啶两侧都是 ≤5000，没有单位。请补 start，并确认 Assay 上限和 ppm 是有意取消还是列错。</t>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>第 10 节及 3.2 标题句</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>The Changed documented are grouped</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Step 1 和 Step 2 仍写 The Changed documented。应为 The documented changes are grouped，或 The changes are grouped。Step 2 的类数已改成 three，与 3.2.2 一致，类数不用再改。</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="72" customHeight="1">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>第 10 节及 3.2 标题句</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>The Changed documented are grouped</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Step 1 和 Step 2 仍写 The Changed documented。应为 The documented changes are grouped，或 The changes are grouped。Step 2 的类数已改成 three，与 3.2.2 一致，类数不用再改。</t>
-        </is>
-      </c>
-    </row>
+    <row r="6" ht="72" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A1:D6"/>
+  <autoFilter ref="A1:D5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
